--- a/testresult.xlsx
+++ b/testresult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A1671A-BD17-F24D-A063-A65E89B35C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAFEB5D-CDA8-B443-8B87-AC3AABA6A3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8380" yWindow="3680" windowWidth="28040" windowHeight="17180" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Type</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>MAR'27</t>
-  </si>
-  <si>
-    <t>ALL</t>
   </si>
   <si>
     <t>Staff</t>
@@ -207,9 +204,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -226,12 +222,9 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -567,216 +560,206 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{151C9BC8-0901-2D49-9889-BA2630F40C73}">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A1" s="1"/>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="N1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8">
+        <v>148</v>
+      </c>
+      <c r="C2" s="8">
+        <v>149</v>
+      </c>
+      <c r="D2" s="8">
+        <v>149</v>
+      </c>
+      <c r="E2" s="8">
+        <v>151</v>
+      </c>
+      <c r="F2" s="8">
+        <v>150</v>
+      </c>
+      <c r="G2" s="8">
+        <v>150</v>
+      </c>
+      <c r="H2" s="8">
+        <v>149</v>
+      </c>
+      <c r="I2" s="8">
+        <v>149</v>
+      </c>
+      <c r="J2" s="8">
+        <v>149</v>
+      </c>
+      <c r="K2" s="8">
+        <v>149</v>
+      </c>
+      <c r="L2" s="8">
+        <v>149</v>
+      </c>
+      <c r="M2" s="8">
+        <v>149</v>
+      </c>
+      <c r="N2" s="8">
+        <v>149</v>
+      </c>
+      <c r="O2" s="8">
+        <v>149</v>
+      </c>
+      <c r="P2" s="8">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="10">
-        <v>148</v>
-      </c>
-      <c r="D2" s="10">
-        <v>149</v>
-      </c>
-      <c r="E2" s="10">
-        <v>149</v>
-      </c>
-      <c r="F2" s="10">
-        <v>151</v>
-      </c>
-      <c r="G2" s="10">
-        <v>150</v>
-      </c>
-      <c r="H2" s="10">
-        <v>150</v>
-      </c>
-      <c r="I2" s="10">
-        <v>149</v>
-      </c>
-      <c r="J2" s="10">
-        <v>149</v>
-      </c>
-      <c r="K2" s="10">
-        <v>149</v>
-      </c>
-      <c r="L2" s="10">
-        <v>149</v>
-      </c>
-      <c r="M2" s="10">
-        <v>149</v>
-      </c>
-      <c r="N2" s="10">
-        <v>149</v>
-      </c>
-      <c r="O2" s="10">
-        <v>149</v>
-      </c>
-      <c r="P2" s="10">
-        <v>149</v>
-      </c>
-      <c r="Q2" s="10">
+      <c r="B3" s="8">
+        <v>149</v>
+      </c>
+      <c r="C3" s="8">
+        <v>149</v>
+      </c>
+      <c r="D3" s="8">
+        <v>149</v>
+      </c>
+      <c r="E3" s="8">
+        <v>149</v>
+      </c>
+      <c r="F3" s="8">
+        <v>149</v>
+      </c>
+      <c r="G3" s="8">
+        <v>149</v>
+      </c>
+      <c r="H3" s="8">
+        <v>149</v>
+      </c>
+      <c r="I3" s="8">
+        <v>149</v>
+      </c>
+      <c r="J3" s="8">
+        <v>149</v>
+      </c>
+      <c r="K3" s="8">
+        <v>149</v>
+      </c>
+      <c r="L3" s="8">
+        <v>149</v>
+      </c>
+      <c r="M3" s="8">
+        <v>149</v>
+      </c>
+      <c r="N3" s="8">
+        <v>149</v>
+      </c>
+      <c r="O3" s="8">
+        <v>149</v>
+      </c>
+      <c r="P3" s="8">
         <v>149</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="12" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="10">
-        <v>149</v>
-      </c>
-      <c r="D3" s="10">
-        <v>149</v>
-      </c>
-      <c r="E3" s="10">
-        <v>149</v>
-      </c>
-      <c r="F3" s="10">
-        <v>149</v>
-      </c>
-      <c r="G3" s="10">
-        <v>149</v>
-      </c>
-      <c r="H3" s="10">
-        <v>149</v>
-      </c>
-      <c r="I3" s="10">
-        <v>149</v>
-      </c>
-      <c r="J3" s="10">
-        <v>149</v>
-      </c>
-      <c r="K3" s="10">
-        <v>149</v>
-      </c>
-      <c r="L3" s="10">
-        <v>149</v>
-      </c>
-      <c r="M3" s="10">
-        <v>149</v>
-      </c>
-      <c r="N3" s="10">
-        <v>149</v>
-      </c>
-      <c r="O3" s="10">
-        <v>149</v>
-      </c>
-      <c r="P3" s="10">
-        <v>149</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="10">
+      <c r="B4" s="8">
         <v>131</v>
       </c>
-      <c r="D4" s="10">
+      <c r="C4" s="8">
         <v>139</v>
       </c>
-      <c r="E4" s="10">
+      <c r="D4" s="8">
         <v>142</v>
       </c>
-      <c r="F4" s="10">
+      <c r="E4" s="8">
         <v>143</v>
       </c>
-      <c r="G4" s="10">
+      <c r="F4" s="8">
         <v>147</v>
       </c>
-      <c r="H4" s="10">
+      <c r="G4" s="8">
         <v>144</v>
       </c>
-      <c r="I4" s="10">
+      <c r="H4" s="8">
         <v>143</v>
       </c>
-      <c r="J4" s="10">
+      <c r="I4" s="8">
         <v>140</v>
       </c>
-      <c r="K4" s="10">
+      <c r="J4" s="8">
         <v>139</v>
       </c>
-      <c r="L4" s="10">
+      <c r="K4" s="8">
         <v>132</v>
       </c>
-      <c r="M4" s="10">
+      <c r="L4" s="8">
         <v>130</v>
       </c>
-      <c r="N4" s="10">
+      <c r="M4" s="8">
         <v>130</v>
       </c>
-      <c r="O4" s="10">
+      <c r="N4" s="8">
         <v>105</v>
       </c>
-      <c r="P4" s="10">
+      <c r="O4" s="8">
         <v>104</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="P4" s="8">
         <v>104</v>
       </c>
     </row>

--- a/testresult.xlsx
+++ b/testresult.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAFEB5D-CDA8-B443-8B87-AC3AABA6A3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41859528-B078-1E40-A4C5-94629360E37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8380" yWindow="3680" windowWidth="28040" windowHeight="17180" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="8380" yWindow="3680" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="CPS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
   <si>
     <t>Type</t>
   </si>
@@ -93,6 +94,21 @@
   </si>
   <si>
     <t>Plan</t>
+  </si>
+  <si>
+    <t>StaffCPS</t>
+  </si>
+  <si>
+    <t>Staff AVGCPS</t>
+  </si>
+  <si>
+    <t>PlanCPS</t>
+  </si>
+  <si>
+    <t>JANTest</t>
+  </si>
+  <si>
+    <t>MAR'27Test</t>
   </si>
 </sst>
 </file>
@@ -766,4 +782,214 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594D1181-445D-3746-9BD8-A2C1C6213A7C}">
+  <dimension ref="A1:P4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="8">
+        <v>148</v>
+      </c>
+      <c r="C2" s="8">
+        <v>149</v>
+      </c>
+      <c r="D2" s="8">
+        <v>149</v>
+      </c>
+      <c r="E2" s="8">
+        <v>151</v>
+      </c>
+      <c r="F2" s="8">
+        <v>150</v>
+      </c>
+      <c r="G2" s="8">
+        <v>150</v>
+      </c>
+      <c r="H2" s="8">
+        <v>149</v>
+      </c>
+      <c r="I2" s="8">
+        <v>149</v>
+      </c>
+      <c r="J2" s="8">
+        <v>149</v>
+      </c>
+      <c r="K2" s="8">
+        <v>149</v>
+      </c>
+      <c r="L2" s="8">
+        <v>149</v>
+      </c>
+      <c r="M2" s="8">
+        <v>149</v>
+      </c>
+      <c r="N2" s="8">
+        <v>150</v>
+      </c>
+      <c r="O2" s="8">
+        <v>160</v>
+      </c>
+      <c r="P2" s="8">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="8">
+        <v>149</v>
+      </c>
+      <c r="C3" s="8">
+        <v>149</v>
+      </c>
+      <c r="D3" s="8">
+        <v>149</v>
+      </c>
+      <c r="E3" s="8">
+        <v>149</v>
+      </c>
+      <c r="F3" s="8">
+        <v>149</v>
+      </c>
+      <c r="G3" s="8">
+        <v>149</v>
+      </c>
+      <c r="H3" s="8">
+        <v>149</v>
+      </c>
+      <c r="I3" s="8">
+        <v>149</v>
+      </c>
+      <c r="J3" s="8">
+        <v>149</v>
+      </c>
+      <c r="K3" s="8">
+        <v>149</v>
+      </c>
+      <c r="L3" s="8">
+        <v>149</v>
+      </c>
+      <c r="M3" s="8">
+        <v>149</v>
+      </c>
+      <c r="N3" s="8">
+        <v>149</v>
+      </c>
+      <c r="O3" s="8">
+        <v>149</v>
+      </c>
+      <c r="P3" s="8">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8">
+        <v>2</v>
+      </c>
+      <c r="D4" s="8">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8">
+        <v>143</v>
+      </c>
+      <c r="F4" s="8">
+        <v>147</v>
+      </c>
+      <c r="G4" s="8">
+        <v>144</v>
+      </c>
+      <c r="H4" s="8">
+        <v>143</v>
+      </c>
+      <c r="I4" s="8">
+        <v>140</v>
+      </c>
+      <c r="J4" s="8">
+        <v>139</v>
+      </c>
+      <c r="K4" s="8">
+        <v>132</v>
+      </c>
+      <c r="L4" s="8">
+        <v>130</v>
+      </c>
+      <c r="M4" s="8">
+        <v>130</v>
+      </c>
+      <c r="N4" s="8">
+        <v>105</v>
+      </c>
+      <c r="O4" s="8">
+        <v>104</v>
+      </c>
+      <c r="P4" s="8">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/testresult.xlsx
+++ b/testresult.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41859528-B078-1E40-A4C5-94629360E37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3AFEC8-7CEF-5147-A399-8014C9D3B839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8380" yWindow="3680" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="8380" yWindow="3680" windowWidth="28040" windowHeight="17180" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Test" sheetId="1" r:id="rId1"/>
     <sheet name="CPS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>

--- a/testresult.xlsx
+++ b/testresult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3AFEC8-7CEF-5147-A399-8014C9D3B839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0852531-F956-E74B-99B9-174E7EC00434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8380" yWindow="3680" windowWidth="28040" windowHeight="17180" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="28">
   <si>
     <t>Type</t>
   </si>
@@ -109,13 +109,25 @@
   </si>
   <si>
     <t>MAR'27Test</t>
+  </si>
+  <si>
+    <t>PAYROLL</t>
+  </si>
+  <si>
+    <t>CONTRACTOR</t>
+  </si>
+  <si>
+    <t>OUTSOURCE</t>
+  </si>
+  <si>
+    <t>ALL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -151,8 +163,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -207,6 +225,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -220,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -242,6 +266,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,83 +606,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{151C9BC8-0901-2D49-9889-BA2630F40C73}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="M1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="8">
+      <c r="C2" s="8">
         <v>148</v>
       </c>
-      <c r="C2" s="8">
-        <v>149</v>
-      </c>
       <c r="D2" s="8">
         <v>149</v>
       </c>
       <c r="E2" s="8">
+        <v>149</v>
+      </c>
+      <c r="F2" s="8">
         <v>151</v>
-      </c>
-      <c r="F2" s="8">
-        <v>150</v>
       </c>
       <c r="G2" s="8">
         <v>150</v>
       </c>
       <c r="H2" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I2" s="8">
         <v>149</v>
@@ -678,14 +708,17 @@
       <c r="P2" s="8">
         <v>149</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+      <c r="Q2" s="8">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="8">
-        <v>149</v>
-      </c>
       <c r="C3" s="8">
         <v>149</v>
       </c>
@@ -728,55 +761,538 @@
       <c r="P3" s="8">
         <v>149</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="Q3" s="8">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="8">
+      <c r="C4" s="8">
         <v>131</v>
       </c>
-      <c r="C4" s="8">
+      <c r="D4" s="8">
         <v>139</v>
       </c>
-      <c r="D4" s="8">
+      <c r="E4" s="8">
         <v>142</v>
       </c>
-      <c r="E4" s="8">
+      <c r="F4" s="8">
         <v>143</v>
       </c>
-      <c r="F4" s="8">
+      <c r="G4" s="8">
         <v>147</v>
       </c>
-      <c r="G4" s="8">
+      <c r="H4" s="8">
         <v>144</v>
       </c>
-      <c r="H4" s="8">
+      <c r="I4" s="8">
         <v>143</v>
       </c>
-      <c r="I4" s="8">
+      <c r="J4" s="8">
         <v>140</v>
       </c>
-      <c r="J4" s="8">
+      <c r="K4" s="8">
         <v>139</v>
       </c>
-      <c r="K4" s="8">
+      <c r="L4" s="8">
         <v>132</v>
-      </c>
-      <c r="L4" s="8">
-        <v>130</v>
       </c>
       <c r="M4" s="8">
         <v>130</v>
       </c>
       <c r="N4" s="8">
+        <v>130</v>
+      </c>
+      <c r="O4" s="8">
         <v>105</v>
-      </c>
-      <c r="O4" s="8">
-        <v>104</v>
       </c>
       <c r="P4" s="8">
         <v>104</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="8">
+        <v>121</v>
+      </c>
+      <c r="D5" s="8">
+        <v>120</v>
+      </c>
+      <c r="E5" s="8">
+        <v>118</v>
+      </c>
+      <c r="F5" s="8">
+        <v>118</v>
+      </c>
+      <c r="G5" s="8">
+        <v>117</v>
+      </c>
+      <c r="H5" s="8">
+        <v>117</v>
+      </c>
+      <c r="I5" s="8">
+        <v>116</v>
+      </c>
+      <c r="J5" s="8">
+        <v>116</v>
+      </c>
+      <c r="K5" s="8">
+        <v>116</v>
+      </c>
+      <c r="L5" s="8">
+        <v>116</v>
+      </c>
+      <c r="M5" s="8">
+        <v>116</v>
+      </c>
+      <c r="N5" s="8">
+        <v>116</v>
+      </c>
+      <c r="O5" s="8">
+        <v>116</v>
+      </c>
+      <c r="P5" s="8">
+        <v>116</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="8">
+        <v>117</v>
+      </c>
+      <c r="D6" s="8">
+        <v>117</v>
+      </c>
+      <c r="E6" s="8">
+        <v>117</v>
+      </c>
+      <c r="F6" s="8">
+        <v>116</v>
+      </c>
+      <c r="G6" s="8">
+        <v>116</v>
+      </c>
+      <c r="H6" s="8">
+        <v>116</v>
+      </c>
+      <c r="I6" s="8">
+        <v>116</v>
+      </c>
+      <c r="J6" s="8">
+        <v>116</v>
+      </c>
+      <c r="K6" s="8">
+        <v>116</v>
+      </c>
+      <c r="L6" s="8">
+        <v>116</v>
+      </c>
+      <c r="M6" s="8">
+        <v>116</v>
+      </c>
+      <c r="N6" s="8">
+        <v>116</v>
+      </c>
+      <c r="O6" s="8">
+        <v>116</v>
+      </c>
+      <c r="P6" s="8">
+        <v>116</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="8">
+        <v>105</v>
+      </c>
+      <c r="D7" s="8">
+        <v>111</v>
+      </c>
+      <c r="E7" s="8">
+        <v>111</v>
+      </c>
+      <c r="F7" s="8">
+        <v>112</v>
+      </c>
+      <c r="G7" s="8">
+        <v>113</v>
+      </c>
+      <c r="H7" s="8">
+        <v>111</v>
+      </c>
+      <c r="I7" s="8">
+        <v>108</v>
+      </c>
+      <c r="J7" s="8">
+        <v>105</v>
+      </c>
+      <c r="K7" s="8">
+        <v>103</v>
+      </c>
+      <c r="L7" s="8">
+        <v>100</v>
+      </c>
+      <c r="M7" s="8">
+        <v>99</v>
+      </c>
+      <c r="N7" s="8">
+        <v>98</v>
+      </c>
+      <c r="O7" s="8">
+        <v>81</v>
+      </c>
+      <c r="P7" s="8">
+        <v>81</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="8">
+        <v>21</v>
+      </c>
+      <c r="D8" s="8">
+        <v>21</v>
+      </c>
+      <c r="E8" s="8">
+        <v>21</v>
+      </c>
+      <c r="F8" s="8">
+        <v>21</v>
+      </c>
+      <c r="G8" s="8">
+        <v>21</v>
+      </c>
+      <c r="H8" s="8">
+        <v>21</v>
+      </c>
+      <c r="I8" s="8">
+        <v>21</v>
+      </c>
+      <c r="J8" s="8">
+        <v>21</v>
+      </c>
+      <c r="K8" s="8">
+        <v>21</v>
+      </c>
+      <c r="L8" s="8">
+        <v>21</v>
+      </c>
+      <c r="M8" s="8">
+        <v>21</v>
+      </c>
+      <c r="N8" s="8">
+        <v>21</v>
+      </c>
+      <c r="O8" s="8">
+        <v>21</v>
+      </c>
+      <c r="P8" s="8">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="8">
+        <v>21</v>
+      </c>
+      <c r="D9" s="8">
+        <v>21</v>
+      </c>
+      <c r="E9" s="8">
+        <v>21</v>
+      </c>
+      <c r="F9" s="8">
+        <v>21</v>
+      </c>
+      <c r="G9" s="8">
+        <v>21</v>
+      </c>
+      <c r="H9" s="8">
+        <v>21</v>
+      </c>
+      <c r="I9" s="8">
+        <v>21</v>
+      </c>
+      <c r="J9" s="8">
+        <v>21</v>
+      </c>
+      <c r="K9" s="8">
+        <v>21</v>
+      </c>
+      <c r="L9" s="8">
+        <v>21</v>
+      </c>
+      <c r="M9" s="8">
+        <v>21</v>
+      </c>
+      <c r="N9" s="8">
+        <v>21</v>
+      </c>
+      <c r="O9" s="8">
+        <v>21</v>
+      </c>
+      <c r="P9" s="8">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="8">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8">
+        <v>20</v>
+      </c>
+      <c r="E10" s="14">
+        <v>22</v>
+      </c>
+      <c r="F10" s="8">
+        <v>21</v>
+      </c>
+      <c r="G10" s="8">
+        <v>21</v>
+      </c>
+      <c r="H10" s="8">
+        <v>20</v>
+      </c>
+      <c r="I10" s="8">
+        <v>20</v>
+      </c>
+      <c r="J10" s="8">
+        <v>20</v>
+      </c>
+      <c r="K10" s="8">
+        <v>20</v>
+      </c>
+      <c r="L10" s="8">
+        <v>19</v>
+      </c>
+      <c r="M10" s="8">
+        <v>19</v>
+      </c>
+      <c r="N10" s="8">
+        <v>19</v>
+      </c>
+      <c r="O10" s="8">
+        <v>17</v>
+      </c>
+      <c r="P10" s="8">
+        <v>17</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="8">
+        <v>6</v>
+      </c>
+      <c r="D11" s="8">
+        <v>8</v>
+      </c>
+      <c r="E11" s="8">
+        <v>10</v>
+      </c>
+      <c r="F11" s="8">
+        <v>12</v>
+      </c>
+      <c r="G11" s="8">
+        <v>12</v>
+      </c>
+      <c r="H11" s="8">
+        <v>12</v>
+      </c>
+      <c r="I11" s="8">
+        <v>12</v>
+      </c>
+      <c r="J11" s="8">
+        <v>12</v>
+      </c>
+      <c r="K11" s="8">
+        <v>12</v>
+      </c>
+      <c r="L11" s="8">
+        <v>12</v>
+      </c>
+      <c r="M11" s="8">
+        <v>12</v>
+      </c>
+      <c r="N11" s="8">
+        <v>12</v>
+      </c>
+      <c r="O11" s="8">
+        <v>12</v>
+      </c>
+      <c r="P11" s="8">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="8">
+        <v>11</v>
+      </c>
+      <c r="D12" s="8">
+        <v>11</v>
+      </c>
+      <c r="E12" s="8">
+        <v>11</v>
+      </c>
+      <c r="F12" s="8">
+        <v>11</v>
+      </c>
+      <c r="G12" s="8">
+        <v>11</v>
+      </c>
+      <c r="H12" s="8">
+        <v>11</v>
+      </c>
+      <c r="I12" s="8">
+        <v>11</v>
+      </c>
+      <c r="J12" s="8">
+        <v>11</v>
+      </c>
+      <c r="K12" s="8">
+        <v>11</v>
+      </c>
+      <c r="L12" s="8">
+        <v>11</v>
+      </c>
+      <c r="M12" s="8">
+        <v>11</v>
+      </c>
+      <c r="N12" s="8">
+        <v>11</v>
+      </c>
+      <c r="O12" s="8">
+        <v>11</v>
+      </c>
+      <c r="P12" s="8">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="8">
+        <v>6</v>
+      </c>
+      <c r="D13" s="14">
+        <v>8</v>
+      </c>
+      <c r="E13" s="8">
+        <v>10</v>
+      </c>
+      <c r="F13" s="8">
+        <v>10</v>
+      </c>
+      <c r="G13" s="14">
+        <v>12</v>
+      </c>
+      <c r="H13" s="14">
+        <v>14</v>
+      </c>
+      <c r="I13" s="14">
+        <v>15</v>
+      </c>
+      <c r="J13" s="14">
+        <v>15</v>
+      </c>
+      <c r="K13" s="14">
+        <v>16</v>
+      </c>
+      <c r="L13" s="14">
+        <v>12</v>
+      </c>
+      <c r="M13" s="14">
+        <v>12</v>
+      </c>
+      <c r="N13" s="14">
+        <v>12</v>
+      </c>
+      <c r="O13" s="8">
+        <v>7</v>
+      </c>
+      <c r="P13" s="8">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/testresult.xlsx
+++ b/testresult.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0852531-F956-E74B-99B9-174E7EC00434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2731F515-F47F-D04D-A0D0-8001B0EB80A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8380" yWindow="3680" windowWidth="28040" windowHeight="17180" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="21720" yWindow="3660" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test" sheetId="1" r:id="rId1"/>
-    <sheet name="CPS" sheetId="2" r:id="rId2"/>
+    <sheet name="ALL" sheetId="1" r:id="rId1"/>
+    <sheet name="ALL-Graph" sheetId="3" r:id="rId2"/>
+    <sheet name="CPS" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="30">
   <si>
     <t>Type</t>
   </si>
@@ -121,13 +122,19 @@
   </si>
   <si>
     <t>ALL</t>
+  </si>
+  <si>
+    <t>% Plan</t>
+  </si>
+  <si>
+    <t>Available FTE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -166,6 +173,19 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -244,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -272,6 +292,12 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,10 +632,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{151C9BC8-0901-2D49-9889-BA2630F40C73}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="17"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -819,479 +846,657 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="8"/>
+      <c r="B6" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="19">
+        <v>0.88260000000000005</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0.93620000000000003</v>
+      </c>
+      <c r="E6" s="19">
+        <v>0.95589999999999997</v>
+      </c>
+      <c r="F6" s="19">
+        <v>0.94789999999999996</v>
+      </c>
+      <c r="G6" s="19">
+        <v>0.97919999999999996</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0.95830000000000004</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0.95909999999999995</v>
+      </c>
+      <c r="J6" s="19">
+        <v>0.93759999999999999</v>
+      </c>
+      <c r="K6" s="19">
+        <v>0.93179999999999996</v>
+      </c>
+      <c r="L6" s="19">
+        <v>0.88370000000000004</v>
+      </c>
+      <c r="M6" s="19">
+        <v>0.87409999999999999</v>
+      </c>
+      <c r="N6" s="19">
+        <v>0.86939999999999995</v>
+      </c>
+      <c r="O6" s="19">
+        <v>0.70230000000000004</v>
+      </c>
+      <c r="P6" s="19">
+        <v>0.70020000000000004</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>0.70020000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="20">
+        <v>17</v>
+      </c>
+      <c r="D7" s="20">
+        <v>10</v>
+      </c>
+      <c r="E7" s="20">
+        <v>7</v>
+      </c>
+      <c r="F7" s="20">
+        <v>8</v>
+      </c>
+      <c r="G7" s="20">
+        <v>3</v>
+      </c>
+      <c r="H7" s="20">
+        <v>6</v>
+      </c>
+      <c r="I7" s="20">
+        <v>6</v>
+      </c>
+      <c r="J7" s="20">
+        <v>9</v>
+      </c>
+      <c r="K7" s="20">
+        <v>10</v>
+      </c>
+      <c r="L7" s="20">
+        <v>17</v>
+      </c>
+      <c r="M7" s="20">
+        <v>19</v>
+      </c>
+      <c r="N7" s="20">
+        <v>19</v>
+      </c>
+      <c r="O7" s="20">
+        <v>44</v>
+      </c>
+      <c r="P7" s="20">
+        <v>45</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="17"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C9" s="8">
         <v>121</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D9" s="8">
         <v>120</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E9" s="8">
         <v>118</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F9" s="8">
         <v>118</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G9" s="8">
         <v>117</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H9" s="8">
         <v>117</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I9" s="8">
         <v>116</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J9" s="8">
         <v>116</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K9" s="8">
         <v>116</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L9" s="8">
         <v>116</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M9" s="8">
         <v>116</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N9" s="8">
         <v>116</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O9" s="8">
         <v>116</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P9" s="8">
         <v>116</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q9" s="8">
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C10" s="8">
         <v>117</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D10" s="8">
         <v>117</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E10" s="8">
         <v>117</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F10" s="8">
         <v>116</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G10" s="8">
         <v>116</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H10" s="8">
         <v>116</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I10" s="8">
         <v>116</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J10" s="8">
         <v>116</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K10" s="8">
         <v>116</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L10" s="8">
         <v>116</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M10" s="8">
         <v>116</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N10" s="8">
         <v>116</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O10" s="8">
         <v>116</v>
       </c>
-      <c r="P6" s="8">
+      <c r="P10" s="8">
         <v>116</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q10" s="8">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C11" s="8">
         <v>105</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D11" s="8">
         <v>111</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E11" s="8">
         <v>111</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F11" s="8">
         <v>112</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G11" s="8">
         <v>113</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H11" s="8">
         <v>111</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I11" s="8">
         <v>108</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J11" s="8">
         <v>105</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K11" s="8">
         <v>103</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L11" s="8">
         <v>100</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M11" s="8">
         <v>99</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N11" s="8">
         <v>98</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O11" s="8">
         <v>81</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P11" s="8">
         <v>81</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q11" s="8">
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="8"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="8">
-        <v>21</v>
-      </c>
-      <c r="D8" s="8">
-        <v>21</v>
-      </c>
-      <c r="E8" s="8">
-        <v>21</v>
-      </c>
-      <c r="F8" s="8">
-        <v>21</v>
-      </c>
-      <c r="G8" s="8">
-        <v>21</v>
-      </c>
-      <c r="H8" s="8">
-        <v>21</v>
-      </c>
-      <c r="I8" s="8">
-        <v>21</v>
-      </c>
-      <c r="J8" s="8">
-        <v>21</v>
-      </c>
-      <c r="K8" s="8">
-        <v>21</v>
-      </c>
-      <c r="L8" s="8">
-        <v>21</v>
-      </c>
-      <c r="M8" s="8">
-        <v>21</v>
-      </c>
-      <c r="N8" s="8">
-        <v>21</v>
-      </c>
-      <c r="O8" s="8">
-        <v>21</v>
-      </c>
-      <c r="P8" s="8">
-        <v>21</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+      <c r="C13" s="8">
+        <v>21</v>
+      </c>
+      <c r="D13" s="8">
+        <v>21</v>
+      </c>
+      <c r="E13" s="8">
+        <v>21</v>
+      </c>
+      <c r="F13" s="8">
+        <v>21</v>
+      </c>
+      <c r="G13" s="8">
+        <v>21</v>
+      </c>
+      <c r="H13" s="8">
+        <v>21</v>
+      </c>
+      <c r="I13" s="8">
+        <v>21</v>
+      </c>
+      <c r="J13" s="8">
+        <v>21</v>
+      </c>
+      <c r="K13" s="8">
+        <v>21</v>
+      </c>
+      <c r="L13" s="8">
+        <v>21</v>
+      </c>
+      <c r="M13" s="8">
+        <v>21</v>
+      </c>
+      <c r="N13" s="8">
+        <v>21</v>
+      </c>
+      <c r="O13" s="8">
+        <v>21</v>
+      </c>
+      <c r="P13" s="8">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="8">
-        <v>21</v>
-      </c>
-      <c r="D9" s="8">
-        <v>21</v>
-      </c>
-      <c r="E9" s="8">
-        <v>21</v>
-      </c>
-      <c r="F9" s="8">
-        <v>21</v>
-      </c>
-      <c r="G9" s="8">
-        <v>21</v>
-      </c>
-      <c r="H9" s="8">
-        <v>21</v>
-      </c>
-      <c r="I9" s="8">
-        <v>21</v>
-      </c>
-      <c r="J9" s="8">
-        <v>21</v>
-      </c>
-      <c r="K9" s="8">
-        <v>21</v>
-      </c>
-      <c r="L9" s="8">
-        <v>21</v>
-      </c>
-      <c r="M9" s="8">
-        <v>21</v>
-      </c>
-      <c r="N9" s="8">
-        <v>21</v>
-      </c>
-      <c r="O9" s="8">
-        <v>21</v>
-      </c>
-      <c r="P9" s="8">
-        <v>21</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
+      <c r="C14" s="8">
+        <v>21</v>
+      </c>
+      <c r="D14" s="8">
+        <v>21</v>
+      </c>
+      <c r="E14" s="8">
+        <v>21</v>
+      </c>
+      <c r="F14" s="8">
+        <v>21</v>
+      </c>
+      <c r="G14" s="8">
+        <v>21</v>
+      </c>
+      <c r="H14" s="8">
+        <v>21</v>
+      </c>
+      <c r="I14" s="8">
+        <v>21</v>
+      </c>
+      <c r="J14" s="8">
+        <v>21</v>
+      </c>
+      <c r="K14" s="8">
+        <v>21</v>
+      </c>
+      <c r="L14" s="8">
+        <v>21</v>
+      </c>
+      <c r="M14" s="8">
+        <v>21</v>
+      </c>
+      <c r="N14" s="8">
+        <v>21</v>
+      </c>
+      <c r="O14" s="8">
+        <v>21</v>
+      </c>
+      <c r="P14" s="8">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B15" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C15" s="8">
         <v>20</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D15" s="8">
         <v>20</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E15" s="14">
         <v>22</v>
       </c>
-      <c r="F10" s="8">
-        <v>21</v>
-      </c>
-      <c r="G10" s="8">
-        <v>21</v>
-      </c>
-      <c r="H10" s="8">
+      <c r="F15" s="8">
+        <v>21</v>
+      </c>
+      <c r="G15" s="8">
+        <v>21</v>
+      </c>
+      <c r="H15" s="8">
         <v>20</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I15" s="8">
         <v>20</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J15" s="8">
         <v>20</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K15" s="8">
         <v>20</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L15" s="8">
         <v>19</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M15" s="8">
         <v>19</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N15" s="8">
         <v>19</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O15" s="8">
         <v>17</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P15" s="8">
         <v>17</v>
       </c>
-      <c r="Q10" s="8">
+      <c r="Q15" s="8">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="8"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B17" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C17" s="8">
         <v>6</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D17" s="8">
         <v>8</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E17" s="8">
         <v>10</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F17" s="8">
         <v>12</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G17" s="8">
         <v>12</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H17" s="8">
         <v>12</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I17" s="8">
         <v>12</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J17" s="8">
         <v>12</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K17" s="8">
         <v>12</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L17" s="8">
         <v>12</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M17" s="8">
         <v>12</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N17" s="8">
         <v>12</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O17" s="8">
         <v>12</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P17" s="8">
         <v>12</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q17" s="8">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B18" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C18" s="8">
         <v>11</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D18" s="8">
         <v>11</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E18" s="8">
         <v>11</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F18" s="8">
         <v>11</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G18" s="8">
         <v>11</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H18" s="8">
         <v>11</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I18" s="8">
         <v>11</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J18" s="8">
         <v>11</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K18" s="8">
         <v>11</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L18" s="8">
         <v>11</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M18" s="8">
         <v>11</v>
       </c>
-      <c r="N12" s="8">
+      <c r="N18" s="8">
         <v>11</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O18" s="8">
         <v>11</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P18" s="8">
         <v>11</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="Q18" s="8">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="16" t="s">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C19" s="8">
         <v>6</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D19" s="14">
         <v>8</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E19" s="8">
         <v>10</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F19" s="8">
         <v>10</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G19" s="14">
         <v>12</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H19" s="14">
         <v>14</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I19" s="14">
         <v>15</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J19" s="14">
         <v>15</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K19" s="14">
         <v>16</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L19" s="14">
         <v>12</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M19" s="14">
         <v>12</v>
       </c>
-      <c r="N13" s="14">
+      <c r="N19" s="14">
         <v>12</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O19" s="8">
         <v>7</v>
       </c>
-      <c r="P13" s="8">
+      <c r="P19" s="8">
         <v>7</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="Q19" s="8">
         <v>7</v>
       </c>
     </row>
@@ -1301,6 +1506,481 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D240BEDF-2DC8-5B43-A028-CE573B9B779F}">
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" t="str">
+        <f>ALL!B1</f>
+        <v>Type</v>
+      </c>
+      <c r="B1" t="str">
+        <f>ALL!C1</f>
+        <v>JAN</v>
+      </c>
+      <c r="C1" t="str">
+        <f>ALL!D1</f>
+        <v>FEB</v>
+      </c>
+      <c r="D1" t="str">
+        <f>ALL!E1</f>
+        <v>MAR</v>
+      </c>
+      <c r="E1" t="str">
+        <f>ALL!F1</f>
+        <v>APR</v>
+      </c>
+      <c r="F1" t="str">
+        <f>ALL!G1</f>
+        <v>MAY</v>
+      </c>
+      <c r="G1" t="str">
+        <f>ALL!H1</f>
+        <v>JUN</v>
+      </c>
+      <c r="H1" t="str">
+        <f>ALL!I1</f>
+        <v>JUL</v>
+      </c>
+      <c r="I1" t="str">
+        <f>ALL!J1</f>
+        <v>AUG</v>
+      </c>
+      <c r="J1" t="str">
+        <f>ALL!K1</f>
+        <v>SEP</v>
+      </c>
+      <c r="K1" t="str">
+        <f>ALL!L1</f>
+        <v>OCT</v>
+      </c>
+      <c r="L1" t="str">
+        <f>ALL!M1</f>
+        <v>NOV</v>
+      </c>
+      <c r="M1" t="str">
+        <f>ALL!N1</f>
+        <v>DEC</v>
+      </c>
+      <c r="N1" t="str">
+        <f>ALL!O1</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O1" t="str">
+        <f>ALL!P1</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P1" t="str">
+        <f>ALL!Q1</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="str">
+        <f>ALL!B2</f>
+        <v>Staff</v>
+      </c>
+      <c r="B2">
+        <f>ALL!C2</f>
+        <v>148</v>
+      </c>
+      <c r="C2">
+        <f>ALL!D2</f>
+        <v>149</v>
+      </c>
+      <c r="D2">
+        <f>ALL!E2</f>
+        <v>149</v>
+      </c>
+      <c r="E2">
+        <f>ALL!F2</f>
+        <v>151</v>
+      </c>
+      <c r="F2">
+        <f>ALL!G2</f>
+        <v>150</v>
+      </c>
+      <c r="G2">
+        <f>ALL!H2</f>
+        <v>150</v>
+      </c>
+      <c r="H2">
+        <f>ALL!I2</f>
+        <v>149</v>
+      </c>
+      <c r="I2">
+        <f>ALL!J2</f>
+        <v>149</v>
+      </c>
+      <c r="J2">
+        <f>ALL!K2</f>
+        <v>149</v>
+      </c>
+      <c r="K2">
+        <f>ALL!L2</f>
+        <v>149</v>
+      </c>
+      <c r="L2">
+        <f>ALL!M2</f>
+        <v>149</v>
+      </c>
+      <c r="M2">
+        <f>ALL!N2</f>
+        <v>149</v>
+      </c>
+      <c r="N2">
+        <f>ALL!O2</f>
+        <v>149</v>
+      </c>
+      <c r="O2">
+        <f>ALL!P2</f>
+        <v>149</v>
+      </c>
+      <c r="P2">
+        <f>ALL!Q2</f>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" t="str">
+        <f>ALL!B3</f>
+        <v>Staff AVG</v>
+      </c>
+      <c r="B3">
+        <f>ALL!C3</f>
+        <v>149</v>
+      </c>
+      <c r="C3">
+        <f>ALL!D3</f>
+        <v>149</v>
+      </c>
+      <c r="D3">
+        <f>ALL!E3</f>
+        <v>149</v>
+      </c>
+      <c r="E3">
+        <f>ALL!F3</f>
+        <v>149</v>
+      </c>
+      <c r="F3">
+        <f>ALL!G3</f>
+        <v>149</v>
+      </c>
+      <c r="G3">
+        <f>ALL!H3</f>
+        <v>149</v>
+      </c>
+      <c r="H3">
+        <f>ALL!I3</f>
+        <v>149</v>
+      </c>
+      <c r="I3">
+        <f>ALL!J3</f>
+        <v>149</v>
+      </c>
+      <c r="J3">
+        <f>ALL!K3</f>
+        <v>149</v>
+      </c>
+      <c r="K3">
+        <f>ALL!L3</f>
+        <v>149</v>
+      </c>
+      <c r="L3">
+        <f>ALL!M3</f>
+        <v>149</v>
+      </c>
+      <c r="M3">
+        <f>ALL!N3</f>
+        <v>149</v>
+      </c>
+      <c r="N3">
+        <f>ALL!O3</f>
+        <v>149</v>
+      </c>
+      <c r="O3">
+        <f>ALL!P3</f>
+        <v>149</v>
+      </c>
+      <c r="P3">
+        <f>ALL!Q3</f>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" t="str">
+        <f>ALL!B4</f>
+        <v>Plan</v>
+      </c>
+      <c r="B4">
+        <f>ALL!C4</f>
+        <v>131</v>
+      </c>
+      <c r="C4">
+        <f>ALL!D4</f>
+        <v>139</v>
+      </c>
+      <c r="D4">
+        <f>ALL!E4</f>
+        <v>142</v>
+      </c>
+      <c r="E4">
+        <f>ALL!F4</f>
+        <v>143</v>
+      </c>
+      <c r="F4">
+        <f>ALL!G4</f>
+        <v>147</v>
+      </c>
+      <c r="G4">
+        <f>ALL!H4</f>
+        <v>144</v>
+      </c>
+      <c r="H4">
+        <f>ALL!I4</f>
+        <v>143</v>
+      </c>
+      <c r="I4">
+        <f>ALL!J4</f>
+        <v>140</v>
+      </c>
+      <c r="J4">
+        <f>ALL!K4</f>
+        <v>139</v>
+      </c>
+      <c r="K4">
+        <f>ALL!L4</f>
+        <v>132</v>
+      </c>
+      <c r="L4">
+        <f>ALL!M4</f>
+        <v>130</v>
+      </c>
+      <c r="M4">
+        <f>ALL!N4</f>
+        <v>130</v>
+      </c>
+      <c r="N4">
+        <f>ALL!O4</f>
+        <v>105</v>
+      </c>
+      <c r="O4">
+        <f>ALL!P4</f>
+        <v>104</v>
+      </c>
+      <c r="P4">
+        <f>ALL!Q4</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" t="str">
+        <f>ALL!B11</f>
+        <v>PAYROLL</v>
+      </c>
+      <c r="B5">
+        <f>ALL!C11</f>
+        <v>105</v>
+      </c>
+      <c r="C5">
+        <f>ALL!D11</f>
+        <v>111</v>
+      </c>
+      <c r="D5">
+        <f>ALL!E11</f>
+        <v>111</v>
+      </c>
+      <c r="E5">
+        <f>ALL!F11</f>
+        <v>112</v>
+      </c>
+      <c r="F5">
+        <f>ALL!G11</f>
+        <v>113</v>
+      </c>
+      <c r="G5">
+        <f>ALL!H11</f>
+        <v>111</v>
+      </c>
+      <c r="H5">
+        <f>ALL!I11</f>
+        <v>108</v>
+      </c>
+      <c r="I5">
+        <f>ALL!J11</f>
+        <v>105</v>
+      </c>
+      <c r="J5">
+        <f>ALL!K11</f>
+        <v>103</v>
+      </c>
+      <c r="K5">
+        <f>ALL!L11</f>
+        <v>100</v>
+      </c>
+      <c r="L5">
+        <f>ALL!M11</f>
+        <v>99</v>
+      </c>
+      <c r="M5">
+        <f>ALL!N11</f>
+        <v>98</v>
+      </c>
+      <c r="N5">
+        <f>ALL!O11</f>
+        <v>81</v>
+      </c>
+      <c r="O5">
+        <f>ALL!P11</f>
+        <v>81</v>
+      </c>
+      <c r="P5">
+        <f>ALL!Q11</f>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" t="str">
+        <f>ALL!B15</f>
+        <v>CONTRACTOR</v>
+      </c>
+      <c r="B6">
+        <f>ALL!C15</f>
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <f>ALL!D15</f>
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <f>ALL!E15</f>
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <f>ALL!F15</f>
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <f>ALL!G15</f>
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <f>ALL!H15</f>
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <f>ALL!I15</f>
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <f>ALL!J15</f>
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <f>ALL!K15</f>
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <f>ALL!L15</f>
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <f>ALL!M15</f>
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <f>ALL!N15</f>
+        <v>19</v>
+      </c>
+      <c r="N6">
+        <f>ALL!O15</f>
+        <v>17</v>
+      </c>
+      <c r="O6">
+        <f>ALL!P15</f>
+        <v>17</v>
+      </c>
+      <c r="P6">
+        <f>ALL!Q15</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <f>ALL!B19</f>
+        <v>OUTSOURCE</v>
+      </c>
+      <c r="B7">
+        <f>ALL!C19</f>
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <f>ALL!D19</f>
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <f>ALL!E19</f>
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <f>ALL!F19</f>
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <f>ALL!G19</f>
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <f>ALL!H19</f>
+        <v>14</v>
+      </c>
+      <c r="H7">
+        <f>ALL!I19</f>
+        <v>15</v>
+      </c>
+      <c r="I7">
+        <f>ALL!J19</f>
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <f>ALL!K19</f>
+        <v>16</v>
+      </c>
+      <c r="K7">
+        <f>ALL!L19</f>
+        <v>12</v>
+      </c>
+      <c r="L7">
+        <f>ALL!M19</f>
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <f>ALL!N19</f>
+        <v>12</v>
+      </c>
+      <c r="N7">
+        <f>ALL!O19</f>
+        <v>7</v>
+      </c>
+      <c r="O7">
+        <f>ALL!P19</f>
+        <v>7</v>
+      </c>
+      <c r="P7">
+        <f>ALL!Q19</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594D1181-445D-3746-9BD8-A2C1C6213A7C}">
   <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/testresult.xlsx
+++ b/testresult.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2731F515-F47F-D04D-A0D0-8001B0EB80A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A65C1F0-0FD5-F04C-823F-576986CB25DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21720" yWindow="3660" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="16760" yWindow="3660" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
-    <sheet name="ALL-Graph" sheetId="3" r:id="rId2"/>
+    <sheet name="ALLGraph" sheetId="3" r:id="rId2"/>
     <sheet name="CPS" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>

--- a/testresult.xlsx
+++ b/testresult.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A65C1F0-0FD5-F04C-823F-576986CB25DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E0FD1B-81A9-0C45-8714-44E63663B53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16760" yWindow="3660" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
-    <sheet name="ALLGraph" sheetId="3" r:id="rId2"/>
+    <sheet name="GraphAll" sheetId="3" r:id="rId2"/>
     <sheet name="CPS" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -1514,10 +1514,6 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" t="str">
-        <f>ALL!B1</f>
-        <v>Type</v>
-      </c>
       <c r="B1" t="str">
         <f>ALL!C1</f>
         <v>JAN</v>
